--- a/artfynd/A 7647-2024 artfynd.xlsx
+++ b/artfynd/A 7647-2024 artfynd.xlsx
@@ -1856,7 +1856,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125629908</v>
+        <v>125632129</v>
       </c>
       <c r="B13" t="n">
         <v>98269</v>
@@ -1889,26 +1889,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>458664</v>
+        <v>458581</v>
       </c>
       <c r="R13" t="n">
-        <v>6901832</v>
+        <v>6901750</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1935,17 +1926,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Döende på hygge.</t>
+          <t>Död knärot.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1972,7 +1963,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125632129</v>
+        <v>125629908</v>
       </c>
       <c r="B14" t="n">
         <v>98269</v>
@@ -2005,17 +1996,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>458581</v>
+        <v>458664</v>
       </c>
       <c r="R14" t="n">
-        <v>6901750</v>
+        <v>6901832</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2042,17 +2042,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Död knärot.</t>
+          <t>Döende på hygge.</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 7647-2024 artfynd.xlsx
+++ b/artfynd/A 7647-2024 artfynd.xlsx
@@ -1540,10 +1540,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125631646</v>
+        <v>125629741</v>
       </c>
       <c r="B10" t="n">
-        <v>98269</v>
+        <v>80029</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1552,25 +1552,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1580,10 +1580,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458602</v>
+        <v>458652</v>
       </c>
       <c r="R10" t="n">
-        <v>6901780</v>
+        <v>6901784</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1610,17 +1610,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>20 exemplar på hygge.</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1647,10 +1642,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125629741</v>
+        <v>125631528</v>
       </c>
       <c r="B11" t="n">
-        <v>80029</v>
+        <v>98269</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1659,25 +1654,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1687,10 +1682,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458652</v>
+        <v>458637</v>
       </c>
       <c r="R11" t="n">
-        <v>6901784</v>
+        <v>6901741</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1717,12 +1712,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>I basväg.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1749,7 +1749,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125631528</v>
+        <v>125631646</v>
       </c>
       <c r="B12" t="n">
         <v>98269</v>
@@ -1789,10 +1789,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>458637</v>
+        <v>458602</v>
       </c>
       <c r="R12" t="n">
-        <v>6901741</v>
+        <v>6901780</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1829,7 +1829,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>I basväg.</t>
+          <t>20 exemplar på hygge.</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 7647-2024 artfynd.xlsx
+++ b/artfynd/A 7647-2024 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125629991</v>
+        <v>125631917</v>
       </c>
       <c r="B2" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80071</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>458666</v>
+        <v>458600</v>
       </c>
       <c r="R2" t="n">
-        <v>6901827</v>
+        <v>6901762</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,17 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Döende på hygge.</t>
+          <t>På sälg som mejats ned.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125631419</v>
+        <v>125629658</v>
       </c>
       <c r="B3" t="n">
-        <v>80029</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>458637</v>
+        <v>458647</v>
       </c>
       <c r="R3" t="n">
-        <v>6901741</v>
+        <v>6901776</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,12 +842,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -889,15 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125632320</v>
+        <v>125632129</v>
       </c>
       <c r="B4" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -929,7 +914,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>458564</v>
+        <v>458581</v>
       </c>
       <c r="R4" t="n">
         <v>6901750</v>
@@ -969,7 +954,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Många knärot under riset på hygge.</t>
+          <t>Död knärot.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,12 +984,7 @@
         <v>125630557</v>
       </c>
       <c r="B5" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,37 +1088,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125631877</v>
+        <v>125629722</v>
       </c>
       <c r="B6" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80071</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1148,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>458602</v>
+        <v>458647</v>
       </c>
       <c r="R6" t="n">
-        <v>6901762</v>
+        <v>6901774</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,17 +1153,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>10 exemplar ute i solen.</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,37 +1185,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125630653</v>
+        <v>125631603</v>
       </c>
       <c r="B7" t="n">
-        <v>80029</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1255,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>458563</v>
+        <v>458608</v>
       </c>
       <c r="R7" t="n">
-        <v>6901799</v>
+        <v>6901785</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1291,6 +1256,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>30 exemplar bleknande på hygget</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,37 +1287,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125631917</v>
+        <v>125632320</v>
       </c>
       <c r="B8" t="n">
-        <v>80029</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1357,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>458600</v>
+        <v>458564</v>
       </c>
       <c r="R8" t="n">
-        <v>6901762</v>
+        <v>6901750</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1362,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På sälg som mejats ned.</t>
+          <t>Många knärot under riset på hygge.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,59 +1389,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125629353</v>
+        <v>125630653</v>
       </c>
       <c r="B9" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80071</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>458607</v>
+        <v>458563</v>
       </c>
       <c r="R9" t="n">
-        <v>6901813</v>
+        <v>6901799</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1503,17 +1454,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Döende bestånd på hygge.</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1540,37 +1486,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125629741</v>
+        <v>125631646</v>
       </c>
       <c r="B10" t="n">
-        <v>80029</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1580,10 +1521,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458652</v>
+        <v>458602</v>
       </c>
       <c r="R10" t="n">
-        <v>6901784</v>
+        <v>6901780</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1610,12 +1551,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>20 exemplar på hygge.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1642,15 +1588,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125631528</v>
+        <v>125629991</v>
       </c>
       <c r="B11" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1682,10 +1623,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458637</v>
+        <v>458666</v>
       </c>
       <c r="R11" t="n">
-        <v>6901741</v>
+        <v>6901827</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1712,17 +1653,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>I basväg.</t>
+          <t>Döende på hygge.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1749,15 +1690,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125631646</v>
+        <v>125631877</v>
       </c>
       <c r="B12" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1792,7 +1728,7 @@
         <v>458602</v>
       </c>
       <c r="R12" t="n">
-        <v>6901780</v>
+        <v>6901762</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1829,7 +1765,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>20 exemplar på hygge.</t>
+          <t>10 exemplar ute i solen.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1856,37 +1792,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125632129</v>
+        <v>125629741</v>
       </c>
       <c r="B13" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80071</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1896,10 +1827,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>458581</v>
+        <v>458652</v>
       </c>
       <c r="R13" t="n">
-        <v>6901750</v>
+        <v>6901784</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1926,17 +1857,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Död knärot.</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1963,59 +1889,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125629908</v>
+        <v>125630239</v>
       </c>
       <c r="B14" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>458664</v>
+        <v>458554</v>
       </c>
       <c r="R14" t="n">
-        <v>6901832</v>
+        <v>6901796</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2048,11 +1960,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Döende på hygge.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2079,50 +1986,54 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125629722</v>
+        <v>125629353</v>
       </c>
       <c r="B15" t="n">
-        <v>80029</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>458647</v>
+        <v>458607</v>
       </c>
       <c r="R15" t="n">
-        <v>6901774</v>
+        <v>6901813</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2155,6 +2066,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Döende bestånd på hygge.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2181,15 +2097,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125629491</v>
+        <v>125629908</v>
       </c>
       <c r="B16" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2216,7 +2127,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2230,10 +2141,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>458638</v>
+        <v>458664</v>
       </c>
       <c r="R16" t="n">
-        <v>6901786</v>
+        <v>6901832</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2270,7 +2181,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>I hyggeskant.</t>
+          <t>Döende på hygge.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2297,37 +2208,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125629658</v>
+        <v>125631528</v>
       </c>
       <c r="B17" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2337,10 +2243,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>458647</v>
+        <v>458637</v>
       </c>
       <c r="R17" t="n">
-        <v>6901776</v>
+        <v>6901741</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2367,17 +2273,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>I hyggeskant.</t>
+          <t>I basväg.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2404,50 +2310,54 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125630239</v>
+        <v>125629491</v>
       </c>
       <c r="B18" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>458554</v>
+        <v>458638</v>
       </c>
       <c r="R18" t="n">
-        <v>6901796</v>
+        <v>6901786</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2480,6 +2390,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>I hyggeskant.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2506,37 +2421,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125631603</v>
+        <v>125631419</v>
       </c>
       <c r="B19" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80071</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2546,10 +2456,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>458608</v>
+        <v>458637</v>
       </c>
       <c r="R19" t="n">
-        <v>6901785</v>
+        <v>6901741</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2586,7 +2496,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>30 exemplar bleknande på hygget</t>
+          <t>I hyggeskant.</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 7647-2024 artfynd.xlsx
+++ b/artfynd/A 7647-2024 artfynd.xlsx
@@ -882,7 +882,7 @@
         <v>125632129</v>
       </c>
       <c r="B4" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125630557</v>
+        <v>125629722</v>
       </c>
       <c r="B5" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,39 +992,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>458551</v>
+        <v>458647</v>
       </c>
       <c r="R5" t="n">
-        <v>6901788</v>
+        <v>6901774</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,17 +1046,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Två sälgar med apothecier i hyggeskant.</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,10 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125629722</v>
+        <v>125630557</v>
       </c>
       <c r="B6" t="n">
-        <v>80071</v>
+        <v>80070</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,34 +1089,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>458647</v>
+        <v>458551</v>
       </c>
       <c r="R6" t="n">
-        <v>6901774</v>
+        <v>6901788</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1153,12 +1148,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Två sälgar med apothecier i hyggeskant.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1188,7 +1188,7 @@
         <v>125631603</v>
       </c>
       <c r="B7" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>125632320</v>
       </c>
       <c r="B8" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>125631646</v>
       </c>
       <c r="B10" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>125629991</v>
       </c>
       <c r="B11" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>125631877</v>
       </c>
       <c r="B12" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1889,45 +1889,54 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125630239</v>
+        <v>125629353</v>
       </c>
       <c r="B14" t="n">
-        <v>80070</v>
+        <v>98331</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>458554</v>
+        <v>458607</v>
       </c>
       <c r="R14" t="n">
-        <v>6901796</v>
+        <v>6901813</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1960,6 +1969,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Döende bestånd på hygge.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1986,54 +2000,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125629353</v>
+        <v>125630239</v>
       </c>
       <c r="B15" t="n">
-        <v>98324</v>
+        <v>80070</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>458607</v>
+        <v>458554</v>
       </c>
       <c r="R15" t="n">
-        <v>6901813</v>
+        <v>6901796</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2066,11 +2071,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Döende bestånd på hygge.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2100,7 +2100,7 @@
         <v>125629908</v>
       </c>
       <c r="B16" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2208,32 +2208,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125631528</v>
+        <v>125631419</v>
       </c>
       <c r="B17" t="n">
-        <v>98324</v>
+        <v>80071</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2283,7 +2283,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>I basväg.</t>
+          <t>I hyggeskant.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2310,10 +2310,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125629491</v>
+        <v>125631528</v>
       </c>
       <c r="B18" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2338,26 +2338,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>458638</v>
+        <v>458637</v>
       </c>
       <c r="R18" t="n">
-        <v>6901786</v>
+        <v>6901741</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2384,17 +2375,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>I hyggeskant.</t>
+          <t>I basväg.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2421,45 +2412,54 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125631419</v>
+        <v>125629491</v>
       </c>
       <c r="B19" t="n">
-        <v>80071</v>
+        <v>98331</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>458637</v>
+        <v>458638</v>
       </c>
       <c r="R19" t="n">
-        <v>6901741</v>
+        <v>6901786</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2486,12 +2486,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">

--- a/artfynd/A 7647-2024 artfynd.xlsx
+++ b/artfynd/A 7647-2024 artfynd.xlsx
@@ -777,32 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125629658</v>
+        <v>125632129</v>
       </c>
       <c r="B3" t="n">
-        <v>80070</v>
+        <v>98331</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>458647</v>
+        <v>458581</v>
       </c>
       <c r="R3" t="n">
-        <v>6901776</v>
+        <v>6901750</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -842,17 +842,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>I hyggeskant.</t>
+          <t>Död knärot.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,32 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125632129</v>
+        <v>125629658</v>
       </c>
       <c r="B4" t="n">
-        <v>98331</v>
+        <v>80070</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>458581</v>
+        <v>458647</v>
       </c>
       <c r="R4" t="n">
-        <v>6901750</v>
+        <v>6901776</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -944,17 +944,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Död knärot.</t>
+          <t>I hyggeskant.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -2208,32 +2208,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125631419</v>
+        <v>125631528</v>
       </c>
       <c r="B17" t="n">
-        <v>80071</v>
+        <v>98331</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2283,7 +2283,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>I hyggeskant.</t>
+          <t>I basväg.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2310,7 +2310,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125631528</v>
+        <v>125629491</v>
       </c>
       <c r="B18" t="n">
         <v>98331</v>
@@ -2338,17 +2338,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>458637</v>
+        <v>458638</v>
       </c>
       <c r="R18" t="n">
-        <v>6901741</v>
+        <v>6901786</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2375,17 +2384,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>I basväg.</t>
+          <t>I hyggeskant.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2412,54 +2421,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125629491</v>
+        <v>125631419</v>
       </c>
       <c r="B19" t="n">
-        <v>98331</v>
+        <v>80071</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>458638</v>
+        <v>458637</v>
       </c>
       <c r="R19" t="n">
-        <v>6901786</v>
+        <v>6901741</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2486,12 +2486,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">

--- a/artfynd/A 7647-2024 artfynd.xlsx
+++ b/artfynd/A 7647-2024 artfynd.xlsx
@@ -777,32 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125632129</v>
+        <v>125629658</v>
       </c>
       <c r="B3" t="n">
-        <v>98331</v>
+        <v>80070</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>458581</v>
+        <v>458647</v>
       </c>
       <c r="R3" t="n">
-        <v>6901750</v>
+        <v>6901776</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -842,17 +842,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Död knärot.</t>
+          <t>I hyggeskant.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,32 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125629658</v>
+        <v>125632129</v>
       </c>
       <c r="B4" t="n">
-        <v>80070</v>
+        <v>98331</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>458647</v>
+        <v>458581</v>
       </c>
       <c r="R4" t="n">
-        <v>6901776</v>
+        <v>6901750</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -944,17 +944,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>I hyggeskant.</t>
+          <t>Död knärot.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 7647-2024 artfynd.xlsx
+++ b/artfynd/A 7647-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125631917</v>
       </c>
       <c r="B2" t="n">
-        <v>80071</v>
+        <v>80072</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -777,32 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125629658</v>
+        <v>125632129</v>
       </c>
       <c r="B3" t="n">
-        <v>80070</v>
+        <v>98334</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>458647</v>
+        <v>458581</v>
       </c>
       <c r="R3" t="n">
-        <v>6901776</v>
+        <v>6901750</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -842,17 +842,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>I hyggeskant.</t>
+          <t>Död knärot.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,32 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125632129</v>
+        <v>125629658</v>
       </c>
       <c r="B4" t="n">
-        <v>98331</v>
+        <v>80071</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>458581</v>
+        <v>458647</v>
       </c>
       <c r="R4" t="n">
-        <v>6901750</v>
+        <v>6901776</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -944,17 +944,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Död knärot.</t>
+          <t>I hyggeskant.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,7 +984,7 @@
         <v>125629722</v>
       </c>
       <c r="B5" t="n">
-        <v>80071</v>
+        <v>80072</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>125630557</v>
       </c>
       <c r="B6" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>125631603</v>
       </c>
       <c r="B7" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>125632320</v>
       </c>
       <c r="B8" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>125630653</v>
       </c>
       <c r="B9" t="n">
-        <v>80071</v>
+        <v>80072</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>125631646</v>
       </c>
       <c r="B10" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>125629991</v>
       </c>
       <c r="B11" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>125631877</v>
       </c>
       <c r="B12" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>125629741</v>
       </c>
       <c r="B13" t="n">
-        <v>80071</v>
+        <v>80072</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1889,54 +1889,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125629353</v>
+        <v>125630239</v>
       </c>
       <c r="B14" t="n">
-        <v>98331</v>
+        <v>80071</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>458607</v>
+        <v>458554</v>
       </c>
       <c r="R14" t="n">
-        <v>6901813</v>
+        <v>6901796</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1969,11 +1960,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Döende bestånd på hygge.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2000,45 +1986,54 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125630239</v>
+        <v>125629353</v>
       </c>
       <c r="B15" t="n">
-        <v>80070</v>
+        <v>98334</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>458554</v>
+        <v>458607</v>
       </c>
       <c r="R15" t="n">
-        <v>6901796</v>
+        <v>6901813</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2071,6 +2066,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Döende bestånd på hygge.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2100,7 +2100,7 @@
         <v>125629908</v>
       </c>
       <c r="B16" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2208,10 +2208,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125631528</v>
+        <v>125629491</v>
       </c>
       <c r="B17" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2236,17 +2236,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>458637</v>
+        <v>458638</v>
       </c>
       <c r="R17" t="n">
-        <v>6901741</v>
+        <v>6901786</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2273,17 +2282,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>I basväg.</t>
+          <t>I hyggeskant.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2310,54 +2319,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125629491</v>
+        <v>125631419</v>
       </c>
       <c r="B18" t="n">
-        <v>98331</v>
+        <v>80072</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>458638</v>
+        <v>458637</v>
       </c>
       <c r="R18" t="n">
-        <v>6901786</v>
+        <v>6901741</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2384,12 +2384,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2421,32 +2421,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125631419</v>
+        <v>125631528</v>
       </c>
       <c r="B19" t="n">
-        <v>80071</v>
+        <v>98334</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2496,7 +2496,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>I hyggeskant.</t>
+          <t>I basväg.</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 7647-2024 artfynd.xlsx
+++ b/artfynd/A 7647-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125631917</v>
       </c>
       <c r="B2" t="n">
-        <v>80072</v>
+        <v>80076</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>125632129</v>
       </c>
       <c r="B3" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>125629658</v>
       </c>
       <c r="B4" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>125629722</v>
       </c>
       <c r="B5" t="n">
-        <v>80072</v>
+        <v>80076</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>125630557</v>
       </c>
       <c r="B6" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>125631603</v>
       </c>
       <c r="B7" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>125632320</v>
       </c>
       <c r="B8" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>125630653</v>
       </c>
       <c r="B9" t="n">
-        <v>80072</v>
+        <v>80076</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>125631646</v>
       </c>
       <c r="B10" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>125629991</v>
       </c>
       <c r="B11" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>125631877</v>
       </c>
       <c r="B12" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>125629741</v>
       </c>
       <c r="B13" t="n">
-        <v>80072</v>
+        <v>80076</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1889,45 +1889,54 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125630239</v>
+        <v>125629353</v>
       </c>
       <c r="B14" t="n">
-        <v>80071</v>
+        <v>98338</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>458554</v>
+        <v>458607</v>
       </c>
       <c r="R14" t="n">
-        <v>6901796</v>
+        <v>6901813</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1960,6 +1969,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Döende bestånd på hygge.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1986,54 +2000,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125629353</v>
+        <v>125630239</v>
       </c>
       <c r="B15" t="n">
-        <v>98334</v>
+        <v>80075</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>458607</v>
+        <v>458554</v>
       </c>
       <c r="R15" t="n">
-        <v>6901813</v>
+        <v>6901796</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2066,11 +2071,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Döende bestånd på hygge.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2100,7 +2100,7 @@
         <v>125629908</v>
       </c>
       <c r="B16" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2208,10 +2208,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125629491</v>
+        <v>125631528</v>
       </c>
       <c r="B17" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2236,26 +2236,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>458638</v>
+        <v>458637</v>
       </c>
       <c r="R17" t="n">
-        <v>6901786</v>
+        <v>6901741</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2282,17 +2273,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>I hyggeskant.</t>
+          <t>I basväg.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2319,45 +2310,54 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125631419</v>
+        <v>125629491</v>
       </c>
       <c r="B18" t="n">
-        <v>80072</v>
+        <v>98338</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>458637</v>
+        <v>458638</v>
       </c>
       <c r="R18" t="n">
-        <v>6901741</v>
+        <v>6901786</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2384,12 +2384,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2421,32 +2421,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125631528</v>
+        <v>125631419</v>
       </c>
       <c r="B19" t="n">
-        <v>98334</v>
+        <v>80076</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2496,7 +2496,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>I basväg.</t>
+          <t>I hyggeskant.</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 7647-2024 artfynd.xlsx
+++ b/artfynd/A 7647-2024 artfynd.xlsx
@@ -2208,32 +2208,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125631528</v>
+        <v>125631419</v>
       </c>
       <c r="B17" t="n">
-        <v>98338</v>
+        <v>80076</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2283,7 +2283,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>I basväg.</t>
+          <t>I hyggeskant.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2310,7 +2310,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125629491</v>
+        <v>125631528</v>
       </c>
       <c r="B18" t="n">
         <v>98338</v>
@@ -2338,26 +2338,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>458638</v>
+        <v>458637</v>
       </c>
       <c r="R18" t="n">
-        <v>6901786</v>
+        <v>6901741</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2384,17 +2375,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>I hyggeskant.</t>
+          <t>I basväg.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2421,45 +2412,54 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125631419</v>
+        <v>125629491</v>
       </c>
       <c r="B19" t="n">
-        <v>80076</v>
+        <v>98338</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>458637</v>
+        <v>458638</v>
       </c>
       <c r="R19" t="n">
-        <v>6901741</v>
+        <v>6901786</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2486,12 +2486,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">

--- a/artfynd/A 7647-2024 artfynd.xlsx
+++ b/artfynd/A 7647-2024 artfynd.xlsx
@@ -777,32 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125632129</v>
+        <v>125629658</v>
       </c>
       <c r="B3" t="n">
-        <v>98338</v>
+        <v>80075</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>458581</v>
+        <v>458647</v>
       </c>
       <c r="R3" t="n">
-        <v>6901750</v>
+        <v>6901776</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -842,17 +842,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Död knärot.</t>
+          <t>I hyggeskant.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,32 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125629658</v>
+        <v>125632129</v>
       </c>
       <c r="B4" t="n">
-        <v>80075</v>
+        <v>98339</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>458647</v>
+        <v>458581</v>
       </c>
       <c r="R4" t="n">
-        <v>6901776</v>
+        <v>6901750</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -944,17 +944,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>I hyggeskant.</t>
+          <t>Död knärot.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125629722</v>
+        <v>125630557</v>
       </c>
       <c r="B5" t="n">
-        <v>80076</v>
+        <v>80075</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,34 +992,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>458647</v>
+        <v>458551</v>
       </c>
       <c r="R5" t="n">
-        <v>6901774</v>
+        <v>6901788</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1046,12 +1051,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Två sälgar med apothecier i hyggeskant.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1078,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125630557</v>
+        <v>125629722</v>
       </c>
       <c r="B6" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1089,39 +1099,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>458551</v>
+        <v>458647</v>
       </c>
       <c r="R6" t="n">
-        <v>6901788</v>
+        <v>6901774</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1148,17 +1153,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Två sälgar med apothecier i hyggeskant.</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1188,7 +1188,7 @@
         <v>125631603</v>
       </c>
       <c r="B7" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>125632320</v>
       </c>
       <c r="B8" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1486,10 +1486,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125631646</v>
+        <v>125629991</v>
       </c>
       <c r="B10" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1521,10 +1521,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458602</v>
+        <v>458666</v>
       </c>
       <c r="R10" t="n">
-        <v>6901780</v>
+        <v>6901827</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1551,17 +1551,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>20 exemplar på hygge.</t>
+          <t>Döende på hygge.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1588,10 +1588,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125629991</v>
+        <v>125631646</v>
       </c>
       <c r="B11" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1623,10 +1623,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458666</v>
+        <v>458602</v>
       </c>
       <c r="R11" t="n">
-        <v>6901827</v>
+        <v>6901780</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1653,17 +1653,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Döende på hygge.</t>
+          <t>20 exemplar på hygge.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1693,7 +1693,7 @@
         <v>125631877</v>
       </c>
       <c r="B12" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>125629353</v>
       </c>
       <c r="B14" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
         <v>125629908</v>
       </c>
       <c r="B16" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2310,10 +2310,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125631528</v>
+        <v>125629491</v>
       </c>
       <c r="B18" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2338,17 +2338,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>458637</v>
+        <v>458638</v>
       </c>
       <c r="R18" t="n">
-        <v>6901741</v>
+        <v>6901786</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2375,17 +2384,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>I basväg.</t>
+          <t>I hyggeskant.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2412,10 +2421,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125629491</v>
+        <v>125631528</v>
       </c>
       <c r="B19" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2440,26 +2449,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>458638</v>
+        <v>458637</v>
       </c>
       <c r="R19" t="n">
-        <v>6901786</v>
+        <v>6901741</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2486,17 +2486,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>I hyggeskant.</t>
+          <t>I basväg.</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 7647-2024 artfynd.xlsx
+++ b/artfynd/A 7647-2024 artfynd.xlsx
@@ -777,32 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125629658</v>
+        <v>125632129</v>
       </c>
       <c r="B3" t="n">
-        <v>80075</v>
+        <v>98339</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>458647</v>
+        <v>458581</v>
       </c>
       <c r="R3" t="n">
-        <v>6901776</v>
+        <v>6901750</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -842,17 +842,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>I hyggeskant.</t>
+          <t>Död knärot.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,32 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125632129</v>
+        <v>125629658</v>
       </c>
       <c r="B4" t="n">
-        <v>98339</v>
+        <v>80075</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>458581</v>
+        <v>458647</v>
       </c>
       <c r="R4" t="n">
-        <v>6901750</v>
+        <v>6901776</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -944,17 +944,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Död knärot.</t>
+          <t>I hyggeskant.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 7647-2024 artfynd.xlsx
+++ b/artfynd/A 7647-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125631917</v>
       </c>
       <c r="B2" t="n">
-        <v>80076</v>
+        <v>80077</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -777,32 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125632129</v>
+        <v>125629658</v>
       </c>
       <c r="B3" t="n">
-        <v>98339</v>
+        <v>80076</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>458581</v>
+        <v>458647</v>
       </c>
       <c r="R3" t="n">
-        <v>6901750</v>
+        <v>6901776</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -842,17 +842,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Död knärot.</t>
+          <t>I hyggeskant.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,32 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125629658</v>
+        <v>125632129</v>
       </c>
       <c r="B4" t="n">
-        <v>80075</v>
+        <v>98341</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>458647</v>
+        <v>458581</v>
       </c>
       <c r="R4" t="n">
-        <v>6901776</v>
+        <v>6901750</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -944,17 +944,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>I hyggeskant.</t>
+          <t>Död knärot.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125630557</v>
+        <v>125629722</v>
       </c>
       <c r="B5" t="n">
-        <v>80075</v>
+        <v>80077</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,39 +992,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>458551</v>
+        <v>458647</v>
       </c>
       <c r="R5" t="n">
-        <v>6901788</v>
+        <v>6901774</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,17 +1046,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Två sälgar med apothecier i hyggeskant.</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,7 +1078,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125629722</v>
+        <v>125630557</v>
       </c>
       <c r="B6" t="n">
         <v>80076</v>
@@ -1099,34 +1089,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>458647</v>
+        <v>458551</v>
       </c>
       <c r="R6" t="n">
-        <v>6901774</v>
+        <v>6901788</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1153,12 +1148,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Två sälgar med apothecier i hyggeskant.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1188,7 +1188,7 @@
         <v>125631603</v>
       </c>
       <c r="B7" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>125632320</v>
       </c>
       <c r="B8" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>125630653</v>
       </c>
       <c r="B9" t="n">
-        <v>80076</v>
+        <v>80077</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,10 +1486,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125629991</v>
+        <v>125631646</v>
       </c>
       <c r="B10" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1521,10 +1521,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458666</v>
+        <v>458602</v>
       </c>
       <c r="R10" t="n">
-        <v>6901827</v>
+        <v>6901780</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1551,17 +1551,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Döende på hygge.</t>
+          <t>20 exemplar på hygge.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1588,10 +1588,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125631646</v>
+        <v>125629991</v>
       </c>
       <c r="B11" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1623,10 +1623,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458602</v>
+        <v>458666</v>
       </c>
       <c r="R11" t="n">
-        <v>6901780</v>
+        <v>6901827</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1653,17 +1653,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>20 exemplar på hygge.</t>
+          <t>Döende på hygge.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1693,7 +1693,7 @@
         <v>125631877</v>
       </c>
       <c r="B12" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>125629741</v>
       </c>
       <c r="B13" t="n">
-        <v>80076</v>
+        <v>80077</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>125629353</v>
       </c>
       <c r="B14" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
         <v>125630239</v>
       </c>
       <c r="B15" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
         <v>125629908</v>
       </c>
       <c r="B16" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2211,7 +2211,7 @@
         <v>125631419</v>
       </c>
       <c r="B17" t="n">
-        <v>80076</v>
+        <v>80077</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2310,10 +2310,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125629491</v>
+        <v>125631528</v>
       </c>
       <c r="B18" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2338,26 +2338,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>458638</v>
+        <v>458637</v>
       </c>
       <c r="R18" t="n">
-        <v>6901786</v>
+        <v>6901741</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2384,17 +2375,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>I hyggeskant.</t>
+          <t>I basväg.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2421,10 +2412,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125631528</v>
+        <v>125629491</v>
       </c>
       <c r="B19" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2449,17 +2440,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>458637</v>
+        <v>458638</v>
       </c>
       <c r="R19" t="n">
-        <v>6901741</v>
+        <v>6901786</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2486,17 +2486,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>I basväg.</t>
+          <t>I hyggeskant.</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 7647-2024 artfynd.xlsx
+++ b/artfynd/A 7647-2024 artfynd.xlsx
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125629722</v>
+        <v>125630557</v>
       </c>
       <c r="B5" t="n">
-        <v>80077</v>
+        <v>80076</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,34 +992,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>458647</v>
+        <v>458551</v>
       </c>
       <c r="R5" t="n">
-        <v>6901774</v>
+        <v>6901788</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1046,12 +1051,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Två sälgar med apothecier i hyggeskant.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1078,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125630557</v>
+        <v>125629722</v>
       </c>
       <c r="B6" t="n">
-        <v>80076</v>
+        <v>80077</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1089,39 +1099,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>458551</v>
+        <v>458647</v>
       </c>
       <c r="R6" t="n">
-        <v>6901788</v>
+        <v>6901774</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1148,17 +1153,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Två sälgar med apothecier i hyggeskant.</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 7647-2024 artfynd.xlsx
+++ b/artfynd/A 7647-2024 artfynd.xlsx
@@ -882,7 +882,7 @@
         <v>125632129</v>
       </c>
       <c r="B4" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>125631603</v>
       </c>
       <c r="B7" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>125632320</v>
       </c>
       <c r="B8" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>125631646</v>
       </c>
       <c r="B10" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>125629991</v>
       </c>
       <c r="B11" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>125631877</v>
       </c>
       <c r="B12" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>125629353</v>
       </c>
       <c r="B14" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
         <v>125629908</v>
       </c>
       <c r="B16" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>125631528</v>
       </c>
       <c r="B18" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>125629491</v>
       </c>
       <c r="B19" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 7647-2024 artfynd.xlsx
+++ b/artfynd/A 7647-2024 artfynd.xlsx
@@ -777,32 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125629658</v>
+        <v>125632129</v>
       </c>
       <c r="B3" t="n">
-        <v>80076</v>
+        <v>98345</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>458647</v>
+        <v>458581</v>
       </c>
       <c r="R3" t="n">
-        <v>6901776</v>
+        <v>6901750</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -842,17 +842,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>I hyggeskant.</t>
+          <t>Död knärot.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,32 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125632129</v>
+        <v>125629658</v>
       </c>
       <c r="B4" t="n">
-        <v>98343</v>
+        <v>80076</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>458581</v>
+        <v>458647</v>
       </c>
       <c r="R4" t="n">
-        <v>6901750</v>
+        <v>6901776</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -944,17 +944,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Död knärot.</t>
+          <t>I hyggeskant.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125630557</v>
+        <v>125629722</v>
       </c>
       <c r="B5" t="n">
-        <v>80076</v>
+        <v>80077</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,39 +992,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>458551</v>
+        <v>458647</v>
       </c>
       <c r="R5" t="n">
-        <v>6901788</v>
+        <v>6901774</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,17 +1046,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Två sälgar med apothecier i hyggeskant.</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,10 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125629722</v>
+        <v>125630557</v>
       </c>
       <c r="B6" t="n">
-        <v>80077</v>
+        <v>80076</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,34 +1089,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>458647</v>
+        <v>458551</v>
       </c>
       <c r="R6" t="n">
-        <v>6901774</v>
+        <v>6901788</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1153,12 +1148,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Två sälgar med apothecier i hyggeskant.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1188,7 +1188,7 @@
         <v>125631603</v>
       </c>
       <c r="B7" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>125632320</v>
       </c>
       <c r="B8" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>125631646</v>
       </c>
       <c r="B10" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>125629991</v>
       </c>
       <c r="B11" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>125631877</v>
       </c>
       <c r="B12" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1889,54 +1889,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125629353</v>
+        <v>125630239</v>
       </c>
       <c r="B14" t="n">
-        <v>98343</v>
+        <v>80076</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>458607</v>
+        <v>458554</v>
       </c>
       <c r="R14" t="n">
-        <v>6901813</v>
+        <v>6901796</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1969,11 +1960,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Döende bestånd på hygge.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2000,45 +1986,54 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125630239</v>
+        <v>125629353</v>
       </c>
       <c r="B15" t="n">
-        <v>80076</v>
+        <v>98345</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>458554</v>
+        <v>458607</v>
       </c>
       <c r="R15" t="n">
-        <v>6901796</v>
+        <v>6901813</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2071,6 +2066,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Döende bestånd på hygge.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2100,7 +2100,7 @@
         <v>125629908</v>
       </c>
       <c r="B16" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2310,10 +2310,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125631528</v>
+        <v>125629491</v>
       </c>
       <c r="B18" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2338,17 +2338,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>458637</v>
+        <v>458638</v>
       </c>
       <c r="R18" t="n">
-        <v>6901741</v>
+        <v>6901786</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2375,17 +2384,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>I basväg.</t>
+          <t>I hyggeskant.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2412,10 +2421,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125629491</v>
+        <v>125631528</v>
       </c>
       <c r="B19" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2440,26 +2449,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>458638</v>
+        <v>458637</v>
       </c>
       <c r="R19" t="n">
-        <v>6901786</v>
+        <v>6901741</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2486,17 +2486,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>I hyggeskant.</t>
+          <t>I basväg.</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 7647-2024 artfynd.xlsx
+++ b/artfynd/A 7647-2024 artfynd.xlsx
@@ -777,32 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125632129</v>
+        <v>125629658</v>
       </c>
       <c r="B3" t="n">
-        <v>98345</v>
+        <v>80076</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>458581</v>
+        <v>458647</v>
       </c>
       <c r="R3" t="n">
-        <v>6901750</v>
+        <v>6901776</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -842,17 +842,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Död knärot.</t>
+          <t>I hyggeskant.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,32 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125629658</v>
+        <v>125632129</v>
       </c>
       <c r="B4" t="n">
-        <v>80076</v>
+        <v>98345</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>458647</v>
+        <v>458581</v>
       </c>
       <c r="R4" t="n">
-        <v>6901776</v>
+        <v>6901750</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -944,17 +944,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>I hyggeskant.</t>
+          <t>Död knärot.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1486,7 +1486,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125631646</v>
+        <v>125629991</v>
       </c>
       <c r="B10" t="n">
         <v>98345</v>
@@ -1521,10 +1521,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458602</v>
+        <v>458666</v>
       </c>
       <c r="R10" t="n">
-        <v>6901780</v>
+        <v>6901827</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1551,17 +1551,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>20 exemplar på hygge.</t>
+          <t>Döende på hygge.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1588,7 +1588,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125629991</v>
+        <v>125631646</v>
       </c>
       <c r="B11" t="n">
         <v>98345</v>
@@ -1623,10 +1623,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458666</v>
+        <v>458602</v>
       </c>
       <c r="R11" t="n">
-        <v>6901827</v>
+        <v>6901780</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1653,17 +1653,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Döende på hygge.</t>
+          <t>20 exemplar på hygge.</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 7647-2024 artfynd.xlsx
+++ b/artfynd/A 7647-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125631917</v>
       </c>
       <c r="B2" t="n">
-        <v>80077</v>
+        <v>80081</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -777,32 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125629658</v>
+        <v>125632129</v>
       </c>
       <c r="B3" t="n">
-        <v>80076</v>
+        <v>98349</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>458647</v>
+        <v>458581</v>
       </c>
       <c r="R3" t="n">
-        <v>6901776</v>
+        <v>6901750</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -842,17 +842,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>I hyggeskant.</t>
+          <t>Död knärot.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,32 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125632129</v>
+        <v>125629658</v>
       </c>
       <c r="B4" t="n">
-        <v>98345</v>
+        <v>80080</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>458581</v>
+        <v>458647</v>
       </c>
       <c r="R4" t="n">
-        <v>6901750</v>
+        <v>6901776</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -944,17 +944,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Död knärot.</t>
+          <t>I hyggeskant.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,7 +984,7 @@
         <v>125629722</v>
       </c>
       <c r="B5" t="n">
-        <v>80077</v>
+        <v>80081</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>125630557</v>
       </c>
       <c r="B6" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>125631603</v>
       </c>
       <c r="B7" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>125632320</v>
       </c>
       <c r="B8" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>125630653</v>
       </c>
       <c r="B9" t="n">
-        <v>80077</v>
+        <v>80081</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,10 +1486,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125629991</v>
+        <v>125631646</v>
       </c>
       <c r="B10" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1521,10 +1521,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458666</v>
+        <v>458602</v>
       </c>
       <c r="R10" t="n">
-        <v>6901827</v>
+        <v>6901780</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1551,17 +1551,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Döende på hygge.</t>
+          <t>20 exemplar på hygge.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1588,10 +1588,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125631646</v>
+        <v>125629991</v>
       </c>
       <c r="B11" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1623,10 +1623,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458602</v>
+        <v>458666</v>
       </c>
       <c r="R11" t="n">
-        <v>6901780</v>
+        <v>6901827</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1653,17 +1653,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>20 exemplar på hygge.</t>
+          <t>Döende på hygge.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1693,7 +1693,7 @@
         <v>125631877</v>
       </c>
       <c r="B12" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>125629741</v>
       </c>
       <c r="B13" t="n">
-        <v>80077</v>
+        <v>80081</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1889,45 +1889,54 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125630239</v>
+        <v>125629353</v>
       </c>
       <c r="B14" t="n">
-        <v>80076</v>
+        <v>98349</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>458554</v>
+        <v>458607</v>
       </c>
       <c r="R14" t="n">
-        <v>6901796</v>
+        <v>6901813</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1960,6 +1969,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Döende bestånd på hygge.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1986,54 +2000,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125629353</v>
+        <v>125630239</v>
       </c>
       <c r="B15" t="n">
-        <v>98345</v>
+        <v>80080</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>458607</v>
+        <v>458554</v>
       </c>
       <c r="R15" t="n">
-        <v>6901813</v>
+        <v>6901796</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2066,11 +2071,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Döende bestånd på hygge.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2100,7 +2100,7 @@
         <v>125629908</v>
       </c>
       <c r="B16" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2211,7 +2211,7 @@
         <v>125631419</v>
       </c>
       <c r="B17" t="n">
-        <v>80077</v>
+        <v>80081</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2310,10 +2310,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125629491</v>
+        <v>125631528</v>
       </c>
       <c r="B18" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2338,26 +2338,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>458638</v>
+        <v>458637</v>
       </c>
       <c r="R18" t="n">
-        <v>6901786</v>
+        <v>6901741</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2384,17 +2375,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>I hyggeskant.</t>
+          <t>I basväg.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2421,10 +2412,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125631528</v>
+        <v>125629491</v>
       </c>
       <c r="B19" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2449,17 +2440,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>458637</v>
+        <v>458638</v>
       </c>
       <c r="R19" t="n">
-        <v>6901741</v>
+        <v>6901786</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2486,17 +2486,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>I basväg.</t>
+          <t>I hyggeskant.</t>
         </is>
       </c>
       <c r="AD19" t="b">
